--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.9%</t>
+          <t>-691.0%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.7%</t>
+          <t>588.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.0%</t>
+          <t>-309.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.4%</t>
+          <t>-172.6%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.240213877034526</v>
+        <v>-3.219997299620176</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076077432645488</v>
+        <v>2.084164063611228</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>0.9939667676841428</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.968899468383531</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.401782302561781</v>
+        <v>-3.381565725147431</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009884072644738</v>
+        <v>2.017970703610478</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8671838438862635</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.891263724314956</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5100829644319</v>
+        <v>-3.48986638701755</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.979637214762609</v>
+        <v>1.987723845728349</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8671838438862635</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.904337131180875</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.603230435735267</v>
+        <v>-3.583013858320917</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934383423024203</v>
+        <v>1.942470053989942</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7241380551893805</v>
+        <v>0.7443546326037307</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810514854745685</v>
+        <v>3.822644801194295</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.63113122284474</v>
+        <v>-3.61091464543039</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.921747149307415</v>
+        <v>1.929833780273155</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6895411310464457</v>
+        <v>0.7097577084607959</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788280741386926</v>
+        <v>3.800410687835536</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.753657325547634</v>
+        <v>-3.733440748133284</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869501152203457</v>
+        <v>1.877587783169197</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5670150283435518</v>
+        <v>0.587231605757902</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711529523742389</v>
+        <v>3.723659470190999</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.984171821733223</v>
+        <v>-3.963955244318872</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.844001313319725</v>
+        <v>1.852087944285465</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3365005321579631</v>
+        <v>0.3567171095723133</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639926785621539</v>
+        <v>3.652056732070149</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.332916906957666</v>
+        <v>-4.312700329543316</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844814998231794</v>
+        <v>1.852901629197534</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2479691556534155</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714989732272048</v>
+        <v>3.727119678720658</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.486903324733807</v>
+        <v>-4.466686747319456</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852200700266978</v>
+        <v>1.860287331232718</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2479691556534155</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783970001417687</v>
+        <v>3.796099947866297</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.436381420906141</v>
+        <v>-4.41616484349179</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858460663918165</v>
+        <v>1.866547294883905</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2479691556534155</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770021203537808</v>
+        <v>3.782151149986418</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.688856574913865</v>
+        <v>-4.668639997499515</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769341091370489</v>
+        <v>1.77742772233623</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2479691556534155</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781891692593222</v>
+        <v>3.794021639041832</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.981752331393277</v>
+        <v>-4.961535753978927</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653393323297668</v>
+        <v>1.661479954263408</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2479691556534155</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783102227112166</v>
+        <v>3.795232173560776</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.168416459528085</v>
+        <v>-5.148199882113735</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582849414271066</v>
+        <v>1.590936045236806</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2010136074145054</v>
+        <v>0.2212301848288556</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771180586844751</v>
+        <v>3.783310533293362</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.314437146442048</v>
+        <v>-5.294220569027697</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519518992241671</v>
+        <v>1.527605623207411</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2121470930349986</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760808584504626</v>
+        <v>3.772938530953237</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.406151155551633</v>
+        <v>-5.385934578137283</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645037445296881</v>
+        <v>1.653124076262621</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2121470930349986</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923012641203671</v>
+        <v>3.935142587652281</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.437802814611603</v>
+        <v>-5.417586237197252</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627223419636707</v>
+        <v>1.635310050602448</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1867620583762082</v>
+        <v>0.2069786357905584</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914758204820821</v>
+        <v>3.926888151269431</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.519737632880486</v>
+        <v>-5.499521055466135</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604678909897645</v>
+        <v>1.612765540863385</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.176827312789128</v>
+        <v>0.1970438902034782</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919026775037064</v>
+        <v>3.931156721485674</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.621713755128893</v>
+        <v>-5.601497177714543</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572814099454185</v>
+        <v>1.580900730419925</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07485119054072042</v>
+        <v>0.09506776795507066</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866766740143922</v>
+        <v>3.878896686592532</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.511707471651672</v>
+        <v>-5.491490894237321</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608969500089248</v>
+        <v>1.617056131054989</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09805576245799563</v>
+        <v>0.1182723398723459</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872842370538462</v>
+        <v>3.884972316987072</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.368647895910746</v>
+        <v>-5.348431318496395</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670443341107593</v>
+        <v>1.678529972073334</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1060691890479749</v>
+        <v>0.1262857664623251</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881900437214424</v>
+        <v>3.894030383663034</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.067201170438908</v>
+        <v>-5.046984593024558</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798282914178864</v>
+        <v>1.806369545144605</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4277324919341624</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070029355380062</v>
+        <v>4.082159301828672</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.091791414674092</v>
+        <v>-5.071574837259742</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789417994237501</v>
+        <v>1.797504625203242</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4277324919341624</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071000533132773</v>
+        <v>4.083130479581383</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.040753038667572</v>
+        <v>-5.020536461253221</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810676249019865</v>
+        <v>1.818762879985605</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4277324919341624</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071843437512529</v>
+        <v>4.083973383961139</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.999613743800941</v>
+        <v>-4.97939716638659</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846170065840663</v>
+        <v>1.854256696806403</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.448655209386443</v>
+        <v>0.4688717868007932</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115565113306652</v>
+        <v>4.127695059755262</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.902978831782301</v>
+        <v>-4.88276225436795</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701008026772053</v>
+        <v>1.709094657737793</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5452901214050829</v>
+        <v>0.5655066988194332</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989730056641771</v>
+        <v>4.001860003090381</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.033559566313143</v>
+        <v>-5.013342988898793</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65227777703368</v>
+        <v>1.660364407999421</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4147093868742404</v>
+        <v>0.4349259642885906</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488365999723</v>
+        <v>3.92701360644584</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.869063232122182</v>
+        <v>-4.848846654707831</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702503129786148</v>
+        <v>1.710589760751888</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5994222984795525</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998008279587889</v>
+        <v>4.010138226036499</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.896433164806614</v>
+        <v>-4.876216587392263</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690742867148805</v>
+        <v>1.698829498114545</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5994222984795525</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997195990024319</v>
+        <v>4.009325936472929</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.906818359696503</v>
+        <v>-4.886601782282153</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696457568317921</v>
+        <v>1.704544199283661</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.568820526175313</v>
+        <v>0.5890371035896632</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000833652215458</v>
+        <v>4.012963598664068</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.925406518418728</v>
+        <v>-4.905189941004378</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759859310605457</v>
+        <v>1.767945941571197</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5502323674530876</v>
+        <v>0.5704489448674379</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060517762758548</v>
+        <v>4.072647709207158</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.925705065114764</v>
+        <v>-4.905488487700413</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756608902745341</v>
+        <v>1.764695533711081</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5499338207570517</v>
+        <v>0.570150398171402</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057207645559225</v>
+        <v>4.069337592007835</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.824881931424336</v>
+        <v>-4.804665354009986</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801469051160903</v>
+        <v>1.809555682126643</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5623980362414055</v>
+        <v>0.5826146136557558</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069217069789229</v>
+        <v>4.081347016237839</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.634100570671929</v>
+        <v>-4.613883993257579</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877910848940409</v>
+        <v>1.885997479906149</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7531793969938129</v>
+        <v>0.7733959744081632</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183815139719216</v>
+        <v>4.195945086167827</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527137212822508</v>
+        <v>-4.506920635408157</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900533037817774</v>
+        <v>1.908619668783515</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8116440049536143</v>
+        <v>0.8318605823679647</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198730750232693</v>
+        <v>4.210860696681304</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471806624920745</v>
+        <v>-4.451590047506395</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.957632209590538</v>
+        <v>1.965718840556278</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8669745928553765</v>
+        <v>0.8871911702697268</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266896039585809</v>
+        <v>4.279025986034419</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459752498007783</v>
+        <v>-4.439535920593432</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.956140428257161</v>
+        <v>1.964227059222901</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8790287197683393</v>
+        <v>0.8992452971826896</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267815083635025</v>
+        <v>4.279945030083635</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.500907617576003</v>
+        <v>-4.480691040161653</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.941559010614008</v>
+        <v>1.949645641579748</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8378736002001184</v>
+        <v>0.8580901776144687</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245002642078228</v>
+        <v>4.257132588526838</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.432859054884474</v>
+        <v>-4.412642477470123</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981629461568502</v>
+        <v>1.989716092534243</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9261387403059985</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298682805571028</v>
+        <v>4.310812752019639</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.664459448053974</v>
+        <v>-4.644242870639624</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909191974474296</v>
+        <v>1.917278605440036</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9261387403059985</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318885475744622</v>
+        <v>4.331015422193233</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.682531956345586</v>
+        <v>-4.662315378931235</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901962971157652</v>
+        <v>1.910049602123392</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9261387403059985</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318885475744622</v>
+        <v>4.331015422193233</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.857638788922031</v>
+        <v>-4.837422211507681</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79217215172054</v>
+        <v>1.80025878268628</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9261387403059985</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.279137389338089</v>
+        <v>4.291267335786699</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943588</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.826352768381576</v>
+        <v>-4.806136190967226</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.811709178933662</v>
+        <v>1.819795809899402</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9372081834321035</v>
+        <v>0.9574247608464539</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.304931620659302</v>
+        <v>4.317061567107912</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.673327376268292</v>
+        <v>-4.653110798853941</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.972090335351881</v>
+        <v>1.980176966317621</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.090233575545388</v>
+        <v>1.110450152959738</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.495917855500178</v>
+        <v>4.508047801948788</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.701634690141562</v>
+        <v>-4.681418112727211</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.148233634710865</v>
+        <v>2.156320265676605</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.090233575545388</v>
+        <v>1.110450152959738</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.683384080408469</v>
+        <v>4.695514026857079</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.868227915255084</v>
+        <v>-4.848011337840734</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.050999296019538</v>
+        <v>2.059085926985278</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9438569278462154</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.552831096694439</v>
+        <v>4.564961043143049</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568381</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.845192121893518</v>
+        <v>-4.824975544479168</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.063890016025882</v>
+        <v>2.071976646991622</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9438569278462154</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.556507499356156</v>
+        <v>4.568637445804766</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.740601586682203</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.815946141437822</v>
+        <v>-4.795729564023471</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.073206463331656</v>
+        <v>2.081293094297396</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9438569278462154</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.554125554479652</v>
+        <v>4.566255500928261</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.699424827539106</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.922871689315673</v>
+        <v>-4.902655111901322</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.027729483338151</v>
+        <v>2.03581611430389</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.816714802554014</v>
+        <v>0.8369313799683641</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.487263464910575</v>
+        <v>4.499393411359185</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983736</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.067890247822922</v>
+        <v>-5.047673670408571</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.971150862078485</v>
+        <v>1.979237493044225</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6716962440467654</v>
+        <v>0.6919128214611155</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.40168113194946</v>
+        <v>4.413811078398071</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969748</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.186232013607639</v>
+        <v>-5.166015436193288</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.023745395022351</v>
+        <v>2.031832025988091</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7025988600240056</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.508023994344947</v>
+        <v>4.520153940793557</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073538</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.237642435928347</v>
+        <v>-5.217425858513996</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.000966923220007</v>
+        <v>2.009053554185747</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7025988600240056</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.505809691470886</v>
+        <v>4.517939637919496</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.317061887136099</v>
+        <v>-5.296845309721748</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.969102270811196</v>
+        <v>1.977188901776936</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7025988600240056</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.505712819545176</v>
+        <v>4.517842765993786</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.412524885053316</v>
+        <v>-5.392308307638966</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.930910965202352</v>
+        <v>1.938997596168092</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7025988600240056</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.505706713103219</v>
+        <v>4.517836659551829</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.4525448830971</v>
+        <v>-5.432328305682749</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.912999362547449</v>
+        <v>1.921085993513189</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.6625788619802218</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.479791110839559</v>
+        <v>4.491921057288169</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636272</v>
+        <v>3.73610959863627</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.507914045229294</v>
+        <v>-5.487697467814943</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.896585515442298</v>
+        <v>1.904672146408039</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.6625788619802218</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.485524928587286</v>
+        <v>4.497654875035896</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396015</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.553351825060121</v>
+        <v>-5.53313524764577</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.8779487668529</v>
+        <v>1.88603539781864</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6197338713020621</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.459356297523323</v>
+        <v>4.471486243971934</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396424</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.465144990912543</v>
+        <v>-5.444928413498192</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.933105893362251</v>
+        <v>1.941192524327991</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6197338713020621</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.479230690373642</v>
+        <v>4.491360636822253</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.288854766307235</v>
+        <v>-5.268638188892885</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.987322683729102</v>
+        <v>1.995409314694842</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6197338713020621</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.462931390898371</v>
+        <v>4.475061337346981</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.10564310317414</v>
+        <v>-5.085426525759789</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.063038298446385</v>
+        <v>2.071124929412125</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6197338713020621</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.465362340362416</v>
+        <v>4.477492286811026</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146288</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.033921656160289</v>
+        <v>-5.013705078745939</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.057518063099815</v>
+        <v>2.065604694065555</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6712387409015627</v>
+        <v>0.6914553183159128</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.474186394418616</v>
+        <v>4.486316340867226</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067685</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.011548630552583</v>
+        <v>-4.991332053138232</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.013383019264069</v>
+        <v>2.021469650229809</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6824944920144642</v>
+        <v>0.7027110694288143</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.427855591007528</v>
+        <v>4.439985537456138</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739467</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.044564926463328</v>
+        <v>-5.024348349048977</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.185374705785127</v>
+        <v>2.193461336750867</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6130571153477127</v>
+        <v>0.6332736927620628</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.571391369892833</v>
+        <v>4.583521316341443</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166413</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.033037290813719</v>
+        <v>-5.012820713399369</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.181906985873219</v>
+        <v>2.189993616838959</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6720577735490751</v>
+        <v>0.6922743509634253</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.598712990641899</v>
+        <v>4.610842937090509</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.130378792156088</v>
+        <v>-5.110162214741737</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.14663849785806</v>
+        <v>2.154725128823801</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6276375913835868</v>
+        <v>0.6478541687979369</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.575728993864395</v>
+        <v>4.587858940313005</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70522126471042</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.216234821496054</v>
+        <v>-5.196018244081704</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.113547168314912</v>
+        <v>2.121633799280652</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5852615221574518</v>
+        <v>0.6054780995718019</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.551554434521552</v>
+        <v>4.563684380970162</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893118</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.199425897096783</v>
+        <v>-5.179209319682433</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.102689939895122</v>
+        <v>2.110776570860862</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6093276178458319</v>
+        <v>0.629544195260182</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.548413293755082</v>
+        <v>4.560543240203692</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950191</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.290808459662242</v>
+        <v>-5.270591882247891</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.076301425913988</v>
+        <v>2.084388056879728</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5179450552803737</v>
+        <v>0.5381616326947238</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.503748267260857</v>
+        <v>4.515878213709467</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.703999067691679</v>
+        <v>3.719760093558268</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.292960824303095</v>
+        <v>-5.294391312338388</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.177568737881915</v>
+        <v>2.176996542667798</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5157926906395204</v>
+        <v>0.5143622026042269</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.604585106300613</v>
+        <v>4.603726813479437</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-691.0%</t>
+          <t>-678.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.5%</t>
+          <t>-153.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.8%</t>
+          <t>588.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.0%</t>
+          <t>-306.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.6%</t>
+          <t>-171.0%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.219997299620176</v>
+        <v>-3.240213877034526</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.084164063611228</v>
+        <v>2.076077432645488</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9939667676841428</v>
+        <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.968899468383531</v>
+        <v>3.956769521934921</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.381565725147431</v>
+        <v>-3.401782302561781</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.017970703610478</v>
+        <v>2.009884072644738</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8671838438862635</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.891263724314956</v>
+        <v>3.879133777866346</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.48986638701755</v>
+        <v>-3.5100829644319</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.987723845728349</v>
+        <v>1.979637214762609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8671838438862635</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.904337131180875</v>
+        <v>3.892207184732265</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.583013858320917</v>
+        <v>-3.603230435735267</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.942470053989942</v>
+        <v>1.934383423024203</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7443546326037307</v>
+        <v>0.7241380551893805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.822644801194295</v>
+        <v>3.810514854745685</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.61091464543039</v>
+        <v>-3.63113122284474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.929833780273155</v>
+        <v>1.921747149307415</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7097577084607959</v>
+        <v>0.6895411310464457</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.800410687835536</v>
+        <v>3.788280741386926</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.733440748133284</v>
+        <v>-3.753657325547634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.877587783169197</v>
+        <v>1.869501152203457</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.587231605757902</v>
+        <v>0.5670150283435518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.723659470190999</v>
+        <v>3.711529523742389</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.963955244318872</v>
+        <v>-3.984171821733223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.852087944285465</v>
+        <v>1.844001313319725</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3567171095723133</v>
+        <v>0.3365005321579631</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.652056732070149</v>
+        <v>3.639926785621539</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.312700329543316</v>
+        <v>-4.332916906957666</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.852901629197534</v>
+        <v>1.844814998231794</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2479691556534155</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.727119678720658</v>
+        <v>3.714989732272048</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.466686747319456</v>
+        <v>-4.486903324733807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.860287331232718</v>
+        <v>1.852200700266978</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2479691556534155</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.796099947866297</v>
+        <v>3.783970001417687</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.41616484349179</v>
+        <v>-4.436381420906141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.866547294883905</v>
+        <v>1.858460663918165</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2479691556534155</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.782151149986418</v>
+        <v>3.770021203537808</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.668639997499515</v>
+        <v>-4.688856574913865</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.77742772233623</v>
+        <v>1.769341091370489</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2479691556534155</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.794021639041832</v>
+        <v>3.781891692593222</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.961535753978927</v>
+        <v>-4.981752331393277</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.661479954263408</v>
+        <v>1.653393323297668</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2479691556534155</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.795232173560776</v>
+        <v>3.783102227112166</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.148199882113735</v>
+        <v>-5.168416459528085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.590936045236806</v>
+        <v>1.582849414271066</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2212301848288556</v>
+        <v>0.2010136074145054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.783310533293362</v>
+        <v>3.771180586844751</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.294220569027697</v>
+        <v>-5.314437146442048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.527605623207411</v>
+        <v>1.519518992241671</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2121470930349986</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.772938530953237</v>
+        <v>3.760808584504626</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.385934578137283</v>
+        <v>-5.406151155551633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.653124076262621</v>
+        <v>1.645037445296881</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2121470930349986</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.935142587652281</v>
+        <v>3.923012641203671</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.417586237197252</v>
+        <v>-5.437802814611603</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.635310050602448</v>
+        <v>1.627223419636707</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2069786357905584</v>
+        <v>0.1867620583762082</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.926888151269431</v>
+        <v>3.914758204820821</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.499521055466135</v>
+        <v>-5.519737632880486</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.612765540863385</v>
+        <v>1.604678909897645</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1970438902034782</v>
+        <v>0.176827312789128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.931156721485674</v>
+        <v>3.919026775037064</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.601497177714543</v>
+        <v>-5.621713755128893</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.580900730419925</v>
+        <v>1.572814099454185</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.09506776795507066</v>
+        <v>0.07485119054072042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.878896686592532</v>
+        <v>3.866766740143922</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.491490894237321</v>
+        <v>-5.511707471651672</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.617056131054989</v>
+        <v>1.608969500089248</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1182723398723459</v>
+        <v>0.09805576245799563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.884972316987072</v>
+        <v>3.872842370538462</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.348431318496395</v>
+        <v>-5.368647895910746</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.678529972073334</v>
+        <v>1.670443341107593</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1262857664623251</v>
+        <v>0.1060691890479749</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.894030383663034</v>
+        <v>3.881900437214424</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.046984593024558</v>
+        <v>-5.067201170438908</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.806369545144605</v>
+        <v>1.798282914178864</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4277324919341624</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.082159301828672</v>
+        <v>4.070029355380062</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.071574837259742</v>
+        <v>-5.091791414674092</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.797504625203242</v>
+        <v>1.789417994237501</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4277324919341624</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.083130479581383</v>
+        <v>4.071000533132773</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.020536461253221</v>
+        <v>-5.040753038667572</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.818762879985605</v>
+        <v>1.810676249019865</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4277324919341624</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.083973383961139</v>
+        <v>4.071843437512529</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.97939716638659</v>
+        <v>-4.999613743800941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.854256696806403</v>
+        <v>1.846170065840663</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4688717868007932</v>
+        <v>0.448655209386443</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.127695059755262</v>
+        <v>4.115565113306652</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.88276225436795</v>
+        <v>-4.902978831782301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.709094657737793</v>
+        <v>1.701008026772053</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5655066988194332</v>
+        <v>0.5452901214050829</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.001860003090381</v>
+        <v>3.989730056641771</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.013342988898793</v>
+        <v>-5.033559566313143</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.660364407999421</v>
+        <v>1.65227777703368</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4349259642885906</v>
+        <v>0.4147093868742404</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.92701360644584</v>
+        <v>3.91488365999723</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.848846654707831</v>
+        <v>-4.869063232122182</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.710589760751888</v>
+        <v>1.702503129786148</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5994222984795525</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.010138226036499</v>
+        <v>3.998008279587889</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.876216587392263</v>
+        <v>-4.787765468633176</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.698829498114545</v>
+        <v>1.73420994561818</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5994222984795525</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.009325936472929</v>
+        <v>3.997195990024319</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.886601782282153</v>
+        <v>-4.798150663523066</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.704544199283661</v>
+        <v>1.739924646787296</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5890371035896632</v>
+        <v>0.568820526175313</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.012963598664068</v>
+        <v>4.000833652215458</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.905189941004378</v>
+        <v>-4.81673882224529</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.767945941571197</v>
+        <v>1.803326389074831</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5704489448674379</v>
+        <v>0.5502323674530876</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.072647709207158</v>
+        <v>4.060517762758548</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.905488487700413</v>
+        <v>-4.817037368941326</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.764695533711081</v>
+        <v>1.800075981214716</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.570150398171402</v>
+        <v>0.5499338207570517</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.069337592007835</v>
+        <v>4.057207645559225</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.804665354009986</v>
+        <v>-4.716214235250899</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.809555682126643</v>
+        <v>1.844936129630278</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5826146136557558</v>
+        <v>0.5623980362414055</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.081347016237839</v>
+        <v>4.069217069789229</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.613883993257579</v>
+        <v>-4.525432874498492</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.885997479906149</v>
+        <v>1.921377927409784</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7733959744081632</v>
+        <v>0.7531793969938129</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.195945086167827</v>
+        <v>4.183815139719216</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.506920635408157</v>
+        <v>-4.41846951664907</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.908619668783515</v>
+        <v>1.94400011628715</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8318605823679647</v>
+        <v>0.8116440049536143</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.210860696681304</v>
+        <v>4.198730750232693</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.451590047506395</v>
+        <v>-4.363138928747308</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.965718840556278</v>
+        <v>2.001099288059913</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8871911702697268</v>
+        <v>0.8669745928553765</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.279025986034419</v>
+        <v>4.266896039585809</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.439535920593432</v>
+        <v>-4.351084801834345</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.964227059222901</v>
+        <v>1.999607506726536</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8992452971826896</v>
+        <v>0.8790287197683393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.279945030083635</v>
+        <v>4.267815083635025</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.480691040161653</v>
+        <v>-4.392239921402566</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.949645641579748</v>
+        <v>1.985026089083383</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8580901776144687</v>
+        <v>0.8378736002001184</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.257132588526838</v>
+        <v>4.245002642078228</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.412642477470123</v>
+        <v>-4.324191358711036</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.989716092534243</v>
+        <v>2.025096540037878</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9261387403059985</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.310812752019639</v>
+        <v>4.298682805571028</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.644242870639624</v>
+        <v>-4.555791751880537</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.917278605440036</v>
+        <v>1.952659052943671</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9261387403059985</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.331015422193233</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.662315378931235</v>
+        <v>-4.573864260172148</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.910049602123392</v>
+        <v>1.945430049627027</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9261387403059985</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.331015422193233</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.837422211507681</v>
+        <v>-4.748971092748594</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.80025878268628</v>
+        <v>1.835639230189915</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9261387403059985</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.291267335786699</v>
+        <v>4.279137389338089</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943586</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.806136190967226</v>
+        <v>-4.717685072208138</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.819795809899402</v>
+        <v>1.855176257403037</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9574247608464539</v>
+        <v>0.9372081834321035</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.317061567107912</v>
+        <v>4.304931620659302</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677823</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.653110798853941</v>
+        <v>-4.564659680094854</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.980176966317621</v>
+        <v>2.015557413821256</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.110450152959738</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.508047801948788</v>
+        <v>4.495917855500178</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073882</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.681418112727211</v>
+        <v>-4.592966993968124</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.156320265676605</v>
+        <v>2.191700713180239</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.110450152959738</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.695514026857079</v>
+        <v>4.683384080408469</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.848011337840734</v>
+        <v>-4.759560219081647</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.059085926985278</v>
+        <v>2.094466374488913</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9438569278462154</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.564961043143049</v>
+        <v>4.552831096694439</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.824975544479168</v>
+        <v>-4.736524425720081</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.071976646991622</v>
+        <v>2.107357094495257</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9438569278462154</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.568637445804766</v>
+        <v>4.556507499356156</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.795729564023471</v>
+        <v>-4.707278445264384</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.081293094297396</v>
+        <v>2.116673541801031</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9438569278462154</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.566255500928261</v>
+        <v>4.554125554479652</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.902655111901322</v>
+        <v>-4.814203993142235</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.03581611430389</v>
+        <v>2.071196561807525</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8369313799683641</v>
+        <v>0.816714802554014</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.499393411359185</v>
+        <v>4.487263464910575</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.047673670408571</v>
+        <v>-4.959222551649484</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.979237493044225</v>
+        <v>2.01461794054786</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6919128214611155</v>
+        <v>0.6716962440467654</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.413811078398071</v>
+        <v>4.40168113194946</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.166015436193288</v>
+        <v>-5.077564317434201</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.031832025988091</v>
+        <v>2.067212473491726</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7025988600240056</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.520153940793557</v>
+        <v>4.508023994344947</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.217425858513996</v>
+        <v>-5.128974739754909</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.009053554185747</v>
+        <v>2.044434001689382</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7025988600240056</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.517939637919496</v>
+        <v>4.505809691470886</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.296845309721748</v>
+        <v>-5.208394190962661</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.977188901776936</v>
+        <v>2.012569349280571</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7025988600240056</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.517842765993786</v>
+        <v>4.505712819545176</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.392308307638966</v>
+        <v>-5.303857188879879</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.938997596168092</v>
+        <v>1.974378043671727</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7025988600240056</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.517836659551829</v>
+        <v>4.505706713103219</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.432328305682749</v>
+        <v>-5.343877186923662</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.921085993513189</v>
+        <v>1.956466441016824</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6625788619802218</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.491921057288169</v>
+        <v>4.479791110839559</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.487697467814943</v>
+        <v>-5.399246349055856</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.904672146408039</v>
+        <v>1.940052593911673</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6625788619802218</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.497654875035896</v>
+        <v>4.485524928587286</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.53313524764577</v>
+        <v>-5.444684128886683</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.88603539781864</v>
+        <v>1.921415845322275</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6197338713020621</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.471486243971934</v>
+        <v>4.459356297523323</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.444928413498192</v>
+        <v>-5.356477294739105</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.941192524327991</v>
+        <v>1.976572971831626</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6197338713020621</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.491360636822253</v>
+        <v>4.479230690373642</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.268638188892885</v>
+        <v>-5.180187070133798</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.995409314694842</v>
+        <v>2.030789762198477</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6197338713020621</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.475061337346981</v>
+        <v>4.462931390898371</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.085426525759789</v>
+        <v>-4.996975407000702</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.071124929412125</v>
+        <v>2.10650537691576</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6197338713020621</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.477492286811026</v>
+        <v>4.465362340362416</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.013705078745939</v>
+        <v>-4.925253959986851</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.065604694065555</v>
+        <v>2.10098514156919</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6914553183159128</v>
+        <v>0.6712387409015627</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.486316340867226</v>
+        <v>4.474186394418616</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.991332053138232</v>
+        <v>-4.902880934379145</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.021469650229809</v>
+        <v>2.056850097733444</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7027110694288143</v>
+        <v>0.6824944920144642</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.439985537456138</v>
+        <v>4.427855591007528</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.024348349048977</v>
+        <v>-4.93589723028989</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.193461336750867</v>
+        <v>2.228841784254501</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6332736927620628</v>
+        <v>0.6130571153477127</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.583521316341443</v>
+        <v>4.571391369892833</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.012820713399369</v>
+        <v>-4.924369594640281</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.189993616838959</v>
+        <v>2.225374064342594</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6922743509634253</v>
+        <v>0.6720577735490751</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.610842937090509</v>
+        <v>4.598712990641899</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.110162214741737</v>
+        <v>-5.02171109598265</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.154725128823801</v>
+        <v>2.190105576327435</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6478541687979369</v>
+        <v>0.6276375913835868</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.587858940313005</v>
+        <v>4.575728993864395</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.196018244081704</v>
+        <v>-5.107567125322617</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.121633799280652</v>
+        <v>2.157014246784287</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6054780995718019</v>
+        <v>0.5852615221574518</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.563684380970162</v>
+        <v>4.551554434521552</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.179209319682433</v>
+        <v>-5.090758200923346</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.110776570860862</v>
+        <v>2.146157018364497</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.629544195260182</v>
+        <v>0.6093276178458319</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.560543240203692</v>
+        <v>4.548413293755082</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.71556459695019</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.270591882247891</v>
+        <v>-5.182140763488804</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.084388056879728</v>
+        <v>2.119768504383363</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5381616326947238</v>
+        <v>0.5179450552803737</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.515878213709467</v>
+        <v>4.503748267260857</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.719760093558268</v>
+        <v>3.842393951892589</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.294391312338388</v>
+        <v>-5.170434045501798</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.176996542667798</v>
+        <v>2.226579449402434</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5143622026042269</v>
+        <v>0.5296517732673801</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.603726813479437</v>
+        <v>4.612900555877329</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>53.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-678.6%</t>
+          <t>-669.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-149.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.9%</t>
+          <t>-305.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-171.0%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943586</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073882</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.343877186923662</v>
+        <v>-5.248262668986546</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.956466441016824</v>
+        <v>1.994712248191671</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.7379768025029882</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.479791110839559</v>
+        <v>4.537159821601829</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.399246349055856</v>
+        <v>-5.303631831118739</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.940052593911673</v>
+        <v>1.97829840108652</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.7379768025029882</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.485524928587286</v>
+        <v>4.542893639349556</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.444684128886683</v>
+        <v>-5.349069610949567</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.921415845322275</v>
+        <v>1.959661652497122</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6951318118248286</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.459356297523323</v>
+        <v>4.516725008285594</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.356477294739105</v>
+        <v>-5.260862776801988</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.976572971831626</v>
+        <v>2.014818779006472</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6951318118248286</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.479230690373642</v>
+        <v>4.536599401135913</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.180187070133798</v>
+        <v>-5.084572552196681</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.030789762198477</v>
+        <v>2.069035569373323</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6951318118248286</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.462931390898371</v>
+        <v>4.520300101660641</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.996975407000702</v>
+        <v>-4.901360889063586</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.10650537691576</v>
+        <v>2.144751184090607</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6951318118248286</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.465362340362416</v>
+        <v>4.522731051124686</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.925253959986851</v>
+        <v>-4.829639442049735</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.10098514156919</v>
+        <v>2.139230948744037</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6712387409015627</v>
+        <v>0.7668532588386793</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.474186394418616</v>
+        <v>4.531555105180885</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.902880934379145</v>
+        <v>-4.807266416442029</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.056850097733444</v>
+        <v>2.095095904908291</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6824944920144642</v>
+        <v>0.7781090099515808</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.427855591007528</v>
+        <v>4.485224301769798</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.93589723028989</v>
+        <v>-4.840282712352773</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.228841784254501</v>
+        <v>2.267087591429348</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6130571153477127</v>
+        <v>0.7086716332848293</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.571391369892833</v>
+        <v>4.628760080655103</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.924369594640281</v>
+        <v>-4.828755076703165</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.225374064342594</v>
+        <v>2.263619871517441</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6720577735490751</v>
+        <v>0.7676722914861918</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.598712990641899</v>
+        <v>4.656081701404169</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.02171109598265</v>
+        <v>-4.926096578045533</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.190105576327435</v>
+        <v>2.228351383502282</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6276375913835868</v>
+        <v>0.7232521093207034</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.575728993864395</v>
+        <v>4.633097704626665</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.107567125322617</v>
+        <v>-5.0119526073855</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.157014246784287</v>
+        <v>2.195260053959133</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5852615221574518</v>
+        <v>0.6808760400945684</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.551554434521552</v>
+        <v>4.608923145283822</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.090758200923346</v>
+        <v>-4.995143682986229</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.146157018364497</v>
+        <v>2.184402825539344</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6093276178458319</v>
+        <v>0.7049421357829485</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.548413293755082</v>
+        <v>4.605782004517352</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71556459695019</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.182140763488804</v>
+        <v>-5.086526245551688</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.119768504383363</v>
+        <v>2.15801431155821</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5179450552803737</v>
+        <v>0.6135595732174903</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.503748267260857</v>
+        <v>4.561116978023127</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.842393951892589</v>
+        <v>3.815935086368405</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.170434045501798</v>
+        <v>-5.074819527564681</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.226579449402434</v>
+        <v>2.26482525657728</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5296517732673801</v>
+        <v>0.6252662912044967</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.612900555877329</v>
+        <v>4.670269266639599</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>122.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-669.1%</t>
+          <t>-684.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-149.7%</t>
+          <t>-155.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.9%</t>
+          <t>-309.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-167.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2076"/>
+  <dimension ref="A1:G2077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.603230435735267</v>
+        <v>-3.552857433864471</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934383423024203</v>
+        <v>1.954532623772521</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7241380551893805</v>
+        <v>0.7623896078100739</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810514854745685</v>
+        <v>3.833465786318101</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.63113122284474</v>
+        <v>-3.580758220973944</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.921747149307415</v>
+        <v>1.941896350055734</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6895411310464457</v>
+        <v>0.7277926836671391</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788280741386926</v>
+        <v>3.811231672959342</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.753657325547634</v>
+        <v>-3.703284323676838</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869501152203457</v>
+        <v>1.889650352951775</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5670150283435518</v>
+        <v>0.6052665809642452</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711529523742389</v>
+        <v>3.734480455314805</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.984171821733223</v>
+        <v>-3.933798819862427</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.844001313319725</v>
+        <v>1.864150514068043</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3365005321579631</v>
+        <v>0.3747520847786565</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639926785621539</v>
+        <v>3.662877717193955</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.332916906957666</v>
+        <v>-4.282543905086871</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844814998231794</v>
+        <v>1.864964198980112</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2660041308597587</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714989732272048</v>
+        <v>3.737940663844463</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.486903324733807</v>
+        <v>-4.436530322863011</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852200700266978</v>
+        <v>1.872349901015296</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2660041308597587</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783970001417687</v>
+        <v>3.806920932990103</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.436381420906141</v>
+        <v>-4.386008419035345</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858460663918165</v>
+        <v>1.878609864666483</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2660041308597587</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770021203537808</v>
+        <v>3.792972135110224</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.688856574913865</v>
+        <v>-4.63848357304307</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769341091370489</v>
+        <v>1.789490292118808</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2660041308597587</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781891692593222</v>
+        <v>3.804842624165638</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.981752331393277</v>
+        <v>-4.931379329522482</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653393323297668</v>
+        <v>1.673542524045986</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2660041308597587</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783102227112166</v>
+        <v>3.806053158684582</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.168416459528085</v>
+        <v>-5.11804345765729</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582849414271066</v>
+        <v>1.602998615019385</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2010136074145054</v>
+        <v>0.2392651600351988</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771180586844751</v>
+        <v>3.794131518417168</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.314437146442048</v>
+        <v>-5.264064144571252</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519518992241671</v>
+        <v>1.539668192989989</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2301820682413419</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760808584504626</v>
+        <v>3.783759516077043</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.406151155551633</v>
+        <v>-5.355778153680838</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645037445296881</v>
+        <v>1.665186646045199</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2301820682413419</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923012641203671</v>
+        <v>3.945963572776087</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.437802814611603</v>
+        <v>-5.387429812740807</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627223419636707</v>
+        <v>1.647372620385025</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1867620583762082</v>
+        <v>0.2250136109969016</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914758204820821</v>
+        <v>3.937709136393237</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.519737632880486</v>
+        <v>-5.46936463100969</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604678909897645</v>
+        <v>1.624828110645963</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.176827312789128</v>
+        <v>0.2150788654098215</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919026775037064</v>
+        <v>3.94197770660948</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.621713755128893</v>
+        <v>-5.571340753258098</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572814099454185</v>
+        <v>1.592963300202503</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07485119054072042</v>
+        <v>0.1131027431614139</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866766740143922</v>
+        <v>3.889717671716338</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.511707471651672</v>
+        <v>-5.461334469780876</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608969500089248</v>
+        <v>1.629118700837567</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09805576245799563</v>
+        <v>0.1363073150786891</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872842370538462</v>
+        <v>3.895793302110878</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.368647895910746</v>
+        <v>-5.31827489403995</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670443341107593</v>
+        <v>1.690592541855911</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1060691890479749</v>
+        <v>0.1443207416686684</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881900437214424</v>
+        <v>3.90485136878684</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.067201170438908</v>
+        <v>-5.016828168568113</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798282914178864</v>
+        <v>1.818432114927182</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4457674671405056</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070029355380062</v>
+        <v>4.092980286952479</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.091791414674092</v>
+        <v>-5.041418412803297</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789417994237501</v>
+        <v>1.809567194985819</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4457674671405056</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071000533132773</v>
+        <v>4.093951464705189</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.040753038667572</v>
+        <v>-4.990380036796776</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810676249019865</v>
+        <v>1.830825449768183</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4457674671405056</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071843437512529</v>
+        <v>4.094794369084944</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.999613743800941</v>
+        <v>-4.949240741930145</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846170065840663</v>
+        <v>1.866319266588981</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.448655209386443</v>
+        <v>0.4869067620071365</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115565113306652</v>
+        <v>4.138516044879069</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.902978831782301</v>
+        <v>-4.852605829911505</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701008026772053</v>
+        <v>1.721157227520371</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5452901214050829</v>
+        <v>0.5835416740257764</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989730056641771</v>
+        <v>4.012680988214187</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.033559566313143</v>
+        <v>-4.983186564442348</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65227777703368</v>
+        <v>1.672426977781999</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4147093868742404</v>
+        <v>0.4529609394949339</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488365999723</v>
+        <v>3.937834591569645</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.869063232122182</v>
+        <v>-4.818690230251386</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702503129786148</v>
+        <v>1.722652330534466</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.6174572736858958</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998008279587889</v>
+        <v>4.020959211160306</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.787765468633176</v>
+        <v>-4.846060162935818</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.73420994561818</v>
+        <v>1.710892067897123</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.6174572736858958</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997195990024319</v>
+        <v>4.020146921596735</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.798150663523066</v>
+        <v>-4.856445357825708</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.739924646787296</v>
+        <v>1.716606769066239</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.568820526175313</v>
+        <v>0.6070720787960064</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000833652215458</v>
+        <v>4.023784583787874</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.81673882224529</v>
+        <v>-4.875033516547933</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.803326389074831</v>
+        <v>1.780008511353775</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5502323674530876</v>
+        <v>0.588483920073781</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060517762758548</v>
+        <v>4.083468694330964</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.817037368941326</v>
+        <v>-4.875332063243969</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.800075981214716</v>
+        <v>1.776758103493659</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5499338207570517</v>
+        <v>0.5881853733777451</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057207645559225</v>
+        <v>4.080158577131641</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.716214235250899</v>
+        <v>-4.774508929553541</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.844936129630278</v>
+        <v>1.821618251909221</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5623980362414055</v>
+        <v>0.600649588862099</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069217069789229</v>
+        <v>4.092168001361644</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.525432874498492</v>
+        <v>-4.583727568801134</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.921377927409784</v>
+        <v>1.898060049688727</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7531793969938129</v>
+        <v>0.7914309496145063</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183815139719216</v>
+        <v>4.206766071291632</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.41846951664907</v>
+        <v>-4.476764210951712</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.94400011628715</v>
+        <v>1.920682238566092</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8116440049536143</v>
+        <v>0.8498955575743078</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198730750232693</v>
+        <v>4.221681681805109</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.363138928747308</v>
+        <v>-4.42143362304995</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.001099288059913</v>
+        <v>1.977781410338856</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8669745928553765</v>
+        <v>0.9052261454760699</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266896039585809</v>
+        <v>4.289846971158226</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.351084801834345</v>
+        <v>-4.409379496136987</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.999607506726536</v>
+        <v>1.976289629005479</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8790287197683393</v>
+        <v>0.9172802723890328</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267815083635025</v>
+        <v>4.29076601520744</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.392239921402566</v>
+        <v>-4.450534615705208</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.985026089083383</v>
+        <v>1.961708211362327</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8378736002001184</v>
+        <v>0.8761251528208118</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245002642078228</v>
+        <v>4.267953573650644</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.324191358711036</v>
+        <v>-4.382486053013678</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.025096540037878</v>
+        <v>2.001778662316821</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9441737155123416</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298682805571028</v>
+        <v>4.321633737143444</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.555791751880537</v>
+        <v>-4.614086446183179</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.952659052943671</v>
+        <v>1.929341175222615</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9441737155123416</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318885475744622</v>
+        <v>4.341836407317039</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.573864260172148</v>
+        <v>-4.63215895447479</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.945430049627027</v>
+        <v>1.92211217190597</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9441737155123416</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318885475744622</v>
+        <v>4.341836407317039</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.748971092748594</v>
+        <v>-4.807265787051236</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.835639230189915</v>
+        <v>1.812321352468858</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9441737155123416</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.279137389338089</v>
+        <v>4.302088320910505</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.717685072208138</v>
+        <v>-4.775979766510781</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.855176257403037</v>
+        <v>1.831858379681981</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9372081834321035</v>
+        <v>0.975459736052797</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.304931620659302</v>
+        <v>4.327882552231719</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.564659680094854</v>
+        <v>-4.622954374397496</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.015557413821256</v>
+        <v>1.992239536100199</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.090233575545388</v>
+        <v>1.128485128166081</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.495917855500178</v>
+        <v>4.518868787072593</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.592966993968124</v>
+        <v>-4.651261688270766</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.191700713180239</v>
+        <v>2.168382835459183</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.090233575545388</v>
+        <v>1.128485128166081</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.683384080408469</v>
+        <v>4.706335011980886</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.759560219081647</v>
+        <v>-4.817854913384289</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.094466374488913</v>
+        <v>2.071148496767856</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9618919030525588</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.552831096694439</v>
+        <v>4.575782028266854</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.736524425720081</v>
+        <v>-4.794819120022723</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.107357094495257</v>
+        <v>2.0840392167742</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9618919030525588</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.556507499356156</v>
+        <v>4.579458430928572</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.707278445264384</v>
+        <v>-4.765573139567026</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.116673541801031</v>
+        <v>2.093355664079974</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9618919030525588</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.554125554479652</v>
+        <v>4.577076486052067</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.814203993142235</v>
+        <v>-4.872498687444877</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.071196561807525</v>
+        <v>2.047878684086469</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.816714802554014</v>
+        <v>0.8549663551747074</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.487263464910575</v>
+        <v>4.510214396482992</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.959222551649484</v>
+        <v>-5.017517245952126</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.01461794054786</v>
+        <v>1.991300062826804</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6716962440467654</v>
+        <v>0.7099477966674589</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.40168113194946</v>
+        <v>4.424632063521877</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.077564317434201</v>
+        <v>-5.135859011736843</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.067212473491726</v>
+        <v>2.04389459577067</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.720633835230349</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.508023994344947</v>
+        <v>4.530974925917364</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.128974739754909</v>
+        <v>-5.187269434057551</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.044434001689382</v>
+        <v>2.021116123968325</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.720633835230349</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.505809691470886</v>
+        <v>4.528760623043302</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.208394190962661</v>
+        <v>-5.266688885265303</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.012569349280571</v>
+        <v>1.989251471559514</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.720633835230349</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.505712819545176</v>
+        <v>4.528663751117592</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.303857188879879</v>
+        <v>-5.362151883182521</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.974378043671727</v>
+        <v>1.95106016595067</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.720633835230349</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.505706713103219</v>
+        <v>4.528657644675635</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.248262668986546</v>
+        <v>-5.402171881226304</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.994712248191671</v>
+        <v>1.933148563295767</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7379768025029882</v>
+        <v>0.6806138371865651</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.537159821601829</v>
+        <v>4.502742042411976</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.303631831118739</v>
+        <v>-5.457541043358498</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.97829840108652</v>
+        <v>1.916734716190617</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7379768025029882</v>
+        <v>0.6806138371865651</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.542893639349556</v>
+        <v>4.508475860159702</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.349069610949567</v>
+        <v>-5.502978823189325</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.959661652497122</v>
+        <v>1.898097967601219</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6951318118248286</v>
+        <v>0.6377688465084055</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.516725008285594</v>
+        <v>4.482307229095739</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.260862776801988</v>
+        <v>-5.414771989041747</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.014818779006472</v>
+        <v>1.953255094110569</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6951318118248286</v>
+        <v>0.6377688465084055</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.536599401135913</v>
+        <v>4.502181621946058</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.084572552196681</v>
+        <v>-5.23848176443644</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.069035569373323</v>
+        <v>2.00747188447742</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6951318118248286</v>
+        <v>0.6377688465084055</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.520300101660641</v>
+        <v>4.485882322470786</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.901360889063586</v>
+        <v>-5.055270101303345</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.144751184090607</v>
+        <v>2.083187499194703</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6951318118248286</v>
+        <v>0.6377688465084055</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.522731051124686</v>
+        <v>4.488313271934832</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.829639442049735</v>
+        <v>-4.983548654289494</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.139230948744037</v>
+        <v>2.077667263848133</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7668532588386793</v>
+        <v>0.7094902935222561</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.531555105180885</v>
+        <v>4.497137325991032</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.807266416442029</v>
+        <v>-4.961175628681787</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.095095904908291</v>
+        <v>2.033532220012387</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7781090099515808</v>
+        <v>0.7207460446351577</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.485224301769798</v>
+        <v>4.450806522579945</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.840282712352773</v>
+        <v>-4.994191924592532</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.267087591429348</v>
+        <v>2.205523906533445</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7086716332848293</v>
+        <v>0.6513086679684061</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.628760080655103</v>
+        <v>4.594342301465248</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.828755076703165</v>
+        <v>-4.982664288942924</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.263619871517441</v>
+        <v>2.202056186621538</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7676722914861918</v>
+        <v>0.7103093261697686</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.656081701404169</v>
+        <v>4.621663922214315</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.926096578045533</v>
+        <v>-5.080005790285292</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.228351383502282</v>
+        <v>2.166787698606378</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7232521093207034</v>
+        <v>0.6658891440042802</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.633097704626665</v>
+        <v>4.598679925436811</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.0119526073855</v>
+        <v>-5.165861819625259</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.195260053959133</v>
+        <v>2.13369636906323</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6808760400945684</v>
+        <v>0.6235130747781452</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.608923145283822</v>
+        <v>4.574505366093968</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.995143682986229</v>
+        <v>-5.149052895225988</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.184402825539344</v>
+        <v>2.12283914064344</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7049421357829485</v>
+        <v>0.6475791704665254</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.605782004517352</v>
+        <v>4.571364225327498</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.086526245551688</v>
+        <v>-5.240435457791446</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.15801431155821</v>
+        <v>2.096450626662306</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6135595732174903</v>
+        <v>0.5561966079010672</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.561116978023127</v>
+        <v>4.526699198833272</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,45 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.815935086368405</v>
+        <v>3.673998560171926</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.074819527564681</v>
+        <v>-5.22872873980444</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.26482525657728</v>
+        <v>2.203261571681377</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6252662912044967</v>
+        <v>0.5679033258880736</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.670269266639599</v>
+        <v>4.635851487449744</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="2" t="n">
+        <v>45539</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>3.715651584080745</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>4.338782370419064</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>-5.22872873980444</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>2.203261571681377</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>0.5679033258880736</v>
+      </c>
+      <c r="G2077" t="n">
+        <v>4.331846167405432</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299176</v>
+        <v>3.794507029299175</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.723809890676846</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739463</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893115</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.715564596950188</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171926</v>
+        <v>3.673998560171925</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.715651584080745</v>
+        <v>3.715651584080744</v>
       </c>
       <c r="C2077" t="n">
         <v>4.338782370419064</v>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>136.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>423.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-684.4%</t>
+          <t>-674.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-151.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.7%</t>
+          <t>587.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-309.5%</t>
+          <t>-307.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.2%</t>
+          <t>-163.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>79.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.552857433864471</v>
+        <v>-3.603230435735267</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.954532623772521</v>
+        <v>1.934383423024203</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7623896078100739</v>
+        <v>0.7241380551893805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.833465786318101</v>
+        <v>3.810514854745685</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.580758220973944</v>
+        <v>-3.63113122284474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.941896350055734</v>
+        <v>1.921747149307415</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7277926836671391</v>
+        <v>0.6895411310464457</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.811231672959342</v>
+        <v>3.788280741386926</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.703284323676838</v>
+        <v>-3.753657325547634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.889650352951775</v>
+        <v>1.869501152203457</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6052665809642452</v>
+        <v>0.5670150283435518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.734480455314805</v>
+        <v>3.711529523742389</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.933798819862427</v>
+        <v>-3.984171821733223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.864150514068043</v>
+        <v>1.844001313319725</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3747520847786565</v>
+        <v>0.3365005321579631</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.662877717193955</v>
+        <v>3.639926785621539</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.282543905086871</v>
+        <v>-4.332916906957666</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.864964198980112</v>
+        <v>1.844814998231794</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2660041308597587</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.737940663844463</v>
+        <v>3.714989732272048</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.436530322863011</v>
+        <v>-4.486903324733807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.872349901015296</v>
+        <v>1.852200700266978</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2660041308597587</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.806920932990103</v>
+        <v>3.783970001417687</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.386008419035345</v>
+        <v>-4.436381420906141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.878609864666483</v>
+        <v>1.858460663918165</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2660041308597587</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.792972135110224</v>
+        <v>3.770021203537808</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.63848357304307</v>
+        <v>-4.688856574913865</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.789490292118808</v>
+        <v>1.769341091370489</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2660041308597587</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.804842624165638</v>
+        <v>3.781891692593222</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.931379329522482</v>
+        <v>-4.981752331393277</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.673542524045986</v>
+        <v>1.653393323297668</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2660041308597587</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.806053158684582</v>
+        <v>3.783102227112166</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.11804345765729</v>
+        <v>-5.168416459528085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.602998615019385</v>
+        <v>1.582849414271066</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2392651600351988</v>
+        <v>0.2010136074145054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.794131518417168</v>
+        <v>3.771180586844751</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.264064144571252</v>
+        <v>-5.314437146442048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.539668192989989</v>
+        <v>1.519518992241671</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2301820682413419</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.783759516077043</v>
+        <v>3.760808584504626</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.355778153680838</v>
+        <v>-5.406151155551633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.665186646045199</v>
+        <v>1.645037445296881</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2301820682413419</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.945963572776087</v>
+        <v>3.923012641203671</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.387429812740807</v>
+        <v>-5.437802814611603</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.647372620385025</v>
+        <v>1.627223419636707</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2250136109969016</v>
+        <v>0.1867620583762082</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.937709136393237</v>
+        <v>3.914758204820821</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.46936463100969</v>
+        <v>-5.519737632880486</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.624828110645963</v>
+        <v>1.604678909897645</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2150788654098215</v>
+        <v>0.176827312789128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.94197770660948</v>
+        <v>3.919026775037064</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.571340753258098</v>
+        <v>-5.621713755128893</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.592963300202503</v>
+        <v>1.572814099454185</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1131027431614139</v>
+        <v>0.07485119054072042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.889717671716338</v>
+        <v>3.866766740143922</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.461334469780876</v>
+        <v>-5.511707471651672</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.629118700837567</v>
+        <v>1.608969500089248</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1363073150786891</v>
+        <v>0.09805576245799563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.895793302110878</v>
+        <v>3.872842370538462</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.31827489403995</v>
+        <v>-5.368647895910746</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.690592541855911</v>
+        <v>1.670443341107593</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1443207416686684</v>
+        <v>0.1060691890479749</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.90485136878684</v>
+        <v>3.881900437214424</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.016828168568113</v>
+        <v>-5.067201170438908</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.818432114927182</v>
+        <v>1.798282914178864</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4457674671405056</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.092980286952479</v>
+        <v>4.070029355380062</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.041418412803297</v>
+        <v>-5.091791414674092</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.809567194985819</v>
+        <v>1.789417994237501</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4457674671405056</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.093951464705189</v>
+        <v>4.071000533132773</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.990380036796776</v>
+        <v>-5.040753038667572</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.830825449768183</v>
+        <v>1.810676249019865</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4457674671405056</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.094794369084944</v>
+        <v>4.071843437512529</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.949240741930145</v>
+        <v>-4.999613743800941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.866319266588981</v>
+        <v>1.846170065840663</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4869067620071365</v>
+        <v>0.448655209386443</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.138516044879069</v>
+        <v>4.115565113306652</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.852605829911505</v>
+        <v>-4.902978831782301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.721157227520371</v>
+        <v>1.701008026772053</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5835416740257764</v>
+        <v>0.5452901214050829</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.012680988214187</v>
+        <v>3.989730056641771</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.983186564442348</v>
+        <v>-5.033559566313143</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672426977781999</v>
+        <v>1.65227777703368</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4529609394949339</v>
+        <v>0.4147093868742404</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.937834591569645</v>
+        <v>3.91488365999723</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.818690230251386</v>
+        <v>-4.869063232122182</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.722652330534466</v>
+        <v>1.702503129786148</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6174572736858958</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.020959211160306</v>
+        <v>3.998008279587889</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.846060162935818</v>
+        <v>-4.896433164806614</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.710892067897123</v>
+        <v>1.690742867148805</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6174572736858958</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.020146921596735</v>
+        <v>3.997195990024319</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.856445357825708</v>
+        <v>-4.906818359696503</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.716606769066239</v>
+        <v>1.696457568317921</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6070720787960064</v>
+        <v>0.568820526175313</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.023784583787874</v>
+        <v>4.000833652215458</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.875033516547933</v>
+        <v>-4.925406518418728</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.780008511353775</v>
+        <v>1.759859310605457</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.588483920073781</v>
+        <v>0.5502323674530876</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.083468694330964</v>
+        <v>4.060517762758548</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.875332063243969</v>
+        <v>-4.925705065114764</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.776758103493659</v>
+        <v>1.756608902745341</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5881853733777451</v>
+        <v>0.5499338207570517</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.080158577131641</v>
+        <v>4.057207645559225</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.774508929553541</v>
+        <v>-4.824881931424336</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.821618251909221</v>
+        <v>1.801469051160903</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.600649588862099</v>
+        <v>0.5623980362414055</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.092168001361644</v>
+        <v>4.069217069789229</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.583727568801134</v>
+        <v>-4.634100570671929</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.898060049688727</v>
+        <v>1.877910848940409</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7914309496145063</v>
+        <v>0.7531793969938129</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.206766071291632</v>
+        <v>4.183815139719216</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.476764210951712</v>
+        <v>-4.506696771750092</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.920682238566092</v>
+        <v>1.908709214246741</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8498955575743078</v>
+        <v>0.8193274427170006</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.221681681805109</v>
+        <v>4.203340812890725</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.42143362304995</v>
+        <v>-4.45136618384833</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.977781410338856</v>
+        <v>1.965808386019504</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9052261454760699</v>
+        <v>0.8746580306187628</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.289846971158226</v>
+        <v>4.271506102243841</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.409379496136987</v>
+        <v>-4.439312056935367</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.976289629005479</v>
+        <v>1.964316604686127</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9172802723890328</v>
+        <v>0.8867121575317256</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.29076601520744</v>
+        <v>4.272425146293056</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.450534615705208</v>
+        <v>-4.480467176503588</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.961708211362327</v>
+        <v>1.949735187042974</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8761251528208118</v>
+        <v>0.8455570379635047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.267953573650644</v>
+        <v>4.24961270473626</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.382486053013678</v>
+        <v>-4.412418613812058</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.001778662316821</v>
+        <v>1.989805637997469</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9441737155123416</v>
+        <v>0.9136056006550345</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.321633737143444</v>
+        <v>4.30329286822906</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.614086446183179</v>
+        <v>-4.644019006981559</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.929341175222615</v>
+        <v>1.917368150903263</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9441737155123416</v>
+        <v>0.9136056006550345</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.341836407317039</v>
+        <v>4.323495538402654</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.63215895447479</v>
+        <v>-4.66209151527317</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.92211217190597</v>
+        <v>1.910139147586618</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9441737155123416</v>
+        <v>0.9136056006550345</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.341836407317039</v>
+        <v>4.323495538402654</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.807265787051236</v>
+        <v>-4.837198347849615</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.812321352468858</v>
+        <v>1.800348328149507</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9441737155123416</v>
+        <v>0.9136056006550345</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.302088320910505</v>
+        <v>4.283747451996121</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.775979766510781</v>
+        <v>-4.80591232730916</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.831858379681981</v>
+        <v>1.819885355362629</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.975459736052797</v>
+        <v>0.9448916211954899</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.327882552231719</v>
+        <v>4.309541683317335</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.622954374397496</v>
+        <v>-4.652886935195875</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.992239536100199</v>
+        <v>1.980266511780847</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.128485128166081</v>
+        <v>1.097917013308774</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.518868787072593</v>
+        <v>4.500527918158209</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.651261688270766</v>
+        <v>-4.681194249069145</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.168382835459183</v>
+        <v>2.156409811139831</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.128485128166081</v>
+        <v>1.097917013308774</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.706335011980886</v>
+        <v>4.687994143066502</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.817854913384289</v>
+        <v>-4.847787474182668</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.071148496767856</v>
+        <v>2.059175472448505</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9618919030525588</v>
+        <v>0.9313237881952514</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.575782028266854</v>
+        <v>4.55744115935247</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.794819120022723</v>
+        <v>-4.824751680821102</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.0840392167742</v>
+        <v>2.072066192454849</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9618919030525588</v>
+        <v>0.9313237881952514</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.579458430928572</v>
+        <v>4.561117562014187</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.765573139567026</v>
+        <v>-4.795505700365405</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.093355664079974</v>
+        <v>2.081382639760623</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9618919030525588</v>
+        <v>0.9313237881952514</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.577076486052067</v>
+        <v>4.558735617137683</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.872498687444877</v>
+        <v>-4.902431248243256</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.047878684086469</v>
+        <v>2.035905659767117</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8549663551747074</v>
+        <v>0.8243982403174001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.510214396482992</v>
+        <v>4.491873527568607</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.017517245952126</v>
+        <v>-5.047449806750505</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.991300062826804</v>
+        <v>1.979327038507452</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7099477966674589</v>
+        <v>0.6793796818101515</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.424632063521877</v>
+        <v>4.406291194607492</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.135859011736843</v>
+        <v>-5.165791572535222</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.04389459577067</v>
+        <v>2.031921571451318</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.720633835230349</v>
+        <v>0.6900657203730416</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.530974925917364</v>
+        <v>4.512634057002979</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.187269434057551</v>
+        <v>-5.21720199485593</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.021116123968325</v>
+        <v>2.009143099648973</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.720633835230349</v>
+        <v>0.6900657203730416</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.528760623043302</v>
+        <v>4.510419754128918</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.266688885265303</v>
+        <v>-5.296621446063682</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.989251471559514</v>
+        <v>1.977278447240162</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.720633835230349</v>
+        <v>0.6900657203730416</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.528663751117592</v>
+        <v>4.510322882203208</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.362151883182521</v>
+        <v>-5.3920844439809</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.95106016595067</v>
+        <v>1.939087141631318</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.720633835230349</v>
+        <v>0.6900657203730416</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.528657644675635</v>
+        <v>4.510316775761251</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.402171881226304</v>
+        <v>-5.432104442024683</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.933148563295767</v>
+        <v>1.921175538976416</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6806138371865651</v>
+        <v>0.6500457223292577</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.502742042411976</v>
+        <v>4.484401173497591</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.457541043358498</v>
+        <v>-5.487473604156877</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.916734716190617</v>
+        <v>1.904761691871265</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6806138371865651</v>
+        <v>0.6500457223292577</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.508475860159702</v>
+        <v>4.490134991245318</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.502978823189325</v>
+        <v>-5.532911383987704</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.898097967601219</v>
+        <v>1.886124943281867</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6377688465084055</v>
+        <v>0.6072007316510981</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.482307229095739</v>
+        <v>4.463966360181355</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396422</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.414771989041747</v>
+        <v>-5.444704549840126</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.953255094110569</v>
+        <v>1.941282069791217</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6377688465084055</v>
+        <v>0.6072007316510981</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.502181621946058</v>
+        <v>4.483840753031674</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299175</v>
+        <v>3.794507029299176</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.23848176443644</v>
+        <v>-5.268414325234819</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.00747188447742</v>
+        <v>1.995498860158068</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6377688465084055</v>
+        <v>0.6072007316510981</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.485882322470786</v>
+        <v>4.467541453556402</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.055270101303345</v>
+        <v>-5.085202662101723</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.083187499194703</v>
+        <v>2.071214474875352</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6377688465084055</v>
+        <v>0.6072007316510981</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.488313271934832</v>
+        <v>4.469972403020448</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.983548654289494</v>
+        <v>-5.013481215087872</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.077667263848133</v>
+        <v>2.065694239528781</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7094902935222561</v>
+        <v>0.6789221786649488</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.497137325991032</v>
+        <v>4.478796457076648</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676846</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.961175628681787</v>
+        <v>-4.991108189480166</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.033532220012387</v>
+        <v>2.021559195693036</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7207460446351577</v>
+        <v>0.6901779297778503</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.450806522579945</v>
+        <v>4.43246565366556</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739463</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.994191924592532</v>
+        <v>-5.024124485390911</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.205523906533445</v>
+        <v>2.193550882214093</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6513086679684061</v>
+        <v>0.6207405531110988</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.594342301465248</v>
+        <v>4.576001432550864</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.982664288942924</v>
+        <v>-5.012596849741302</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.202056186621538</v>
+        <v>2.190083162302186</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7103093261697686</v>
+        <v>0.6797412113124612</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.621663922214315</v>
+        <v>4.603323053299931</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519032</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.080005790285292</v>
+        <v>-5.109938351083671</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.166787698606378</v>
+        <v>2.154814674287027</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6658891440042802</v>
+        <v>0.6353210291469729</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.598679925436811</v>
+        <v>4.580339056522426</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710418</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.165861819625259</v>
+        <v>-5.063655334980409</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.13369636906323</v>
+        <v>2.17457896292117</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6235130747781452</v>
+        <v>0.6628149590431147</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.574505366093968</v>
+        <v>4.59808649665295</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893115</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.149052895225988</v>
+        <v>-5.046846410581138</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.12283914064344</v>
+        <v>2.16372173450138</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6475791704665254</v>
+        <v>0.6868810547314949</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.571364225327498</v>
+        <v>4.594945355886479</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950188</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.240435457791446</v>
+        <v>-5.138228973146597</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.096450626662306</v>
+        <v>2.137333220520246</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5561966079010672</v>
+        <v>0.5954984921660367</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.526699198833272</v>
+        <v>4.550280329392255</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.22872873980444</v>
+        <v>-5.126522255159591</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.203261571681377</v>
+        <v>2.244144165539316</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5679033258880736</v>
+        <v>0.6072052101530431</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.635851487449744</v>
+        <v>4.659432618008727</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.715651584080744</v>
+        <v>3.814748046659991</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.338782370419064</v>
+        <v>4.478376397875146</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.22872873980444</v>
+        <v>-5.126522255159591</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.203261571681377</v>
+        <v>2.244144165539316</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5679033258880736</v>
+        <v>0.6072052101530431</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.331846167405432</v>
+        <v>4.471440194861514</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>127.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.1%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-674.2%</t>
+          <t>-680.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.8%</t>
+          <t>-154.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.4%</t>
+          <t>586.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.9%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>-7.7%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.506696771750092</v>
+        <v>-4.527137212822508</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.908709214246741</v>
+        <v>1.900533037817774</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8193274427170006</v>
+        <v>0.8116440049536143</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.203340812890725</v>
+        <v>4.198730750232693</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.45136618384833</v>
+        <v>-4.406003594734996</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.965808386019504</v>
+        <v>1.983953421664838</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8746580306187628</v>
+        <v>0.9327776230411267</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.271506102243841</v>
+        <v>4.306377857697259</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.439312056935367</v>
+        <v>-4.36442585096593</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.964316604686127</v>
+        <v>1.994271087073901</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8867121575317256</v>
+        <v>0.9743553668101916</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.272425146293056</v>
+        <v>4.325011071860136</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.480467176503588</v>
+        <v>-4.405580970534151</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.949735187042974</v>
+        <v>1.979689669430749</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8455570379635047</v>
+        <v>0.9332002472419707</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.24961270473626</v>
+        <v>4.302198630303339</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.412418613812058</v>
+        <v>-4.337532407842621</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.989805637997469</v>
+        <v>2.019760120385243</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9136056006550345</v>
+        <v>1.001248809933501</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.30329286822906</v>
+        <v>4.35587879379614</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.644019006981559</v>
+        <v>-4.569132801012122</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.917368150903263</v>
+        <v>1.947322633291037</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9136056006550345</v>
+        <v>1.001248809933501</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.323495538402654</v>
+        <v>4.376081463969734</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.66209151527317</v>
+        <v>-4.587205309303734</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.910139147586618</v>
+        <v>1.940093629974393</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9136056006550345</v>
+        <v>1.001248809933501</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.323495538402654</v>
+        <v>4.376081463969734</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.837198347849615</v>
+        <v>-4.762312141880178</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.800348328149507</v>
+        <v>1.830302810537281</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9136056006550345</v>
+        <v>1.001248809933501</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.283747451996121</v>
+        <v>4.336333377563201</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.80591232730916</v>
+        <v>-4.731026121339723</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.819885355362629</v>
+        <v>1.849839837750404</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9448916211954899</v>
+        <v>1.032534830473956</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.309541683317335</v>
+        <v>4.362127608884414</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.652886935195875</v>
+        <v>-4.578000729226439</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.980266511780847</v>
+        <v>2.010220994168622</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.097917013308774</v>
+        <v>1.18556022258724</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.500527918158209</v>
+        <v>4.553113843725288</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.681194249069145</v>
+        <v>-4.606308043099709</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.156409811139831</v>
+        <v>2.186364293527606</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.097917013308774</v>
+        <v>1.18556022258724</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.687994143066502</v>
+        <v>4.740580068633581</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.847787474182668</v>
+        <v>-4.772901268213231</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.059175472448505</v>
+        <v>2.089129954836279</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9313237881952514</v>
+        <v>1.018966997473717</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.55744115935247</v>
+        <v>4.610027084919549</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.824751680821102</v>
+        <v>-4.749865474851665</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.072066192454849</v>
+        <v>2.102020674842623</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9313237881952514</v>
+        <v>1.018966997473717</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.561117562014187</v>
+        <v>4.613703487581267</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.795505700365405</v>
+        <v>-4.720619494395969</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.081382639760623</v>
+        <v>2.111337122148397</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9313237881952514</v>
+        <v>1.018966997473717</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.558735617137683</v>
+        <v>4.611321542704762</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.902431248243256</v>
+        <v>-4.82754504227382</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.035905659767117</v>
+        <v>2.065860142154892</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8243982403174001</v>
+        <v>0.9120414495958661</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.491873527568607</v>
+        <v>4.544459453135687</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.047449806750505</v>
+        <v>-4.972563600781069</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.979327038507452</v>
+        <v>2.009281520895226</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6793796818101515</v>
+        <v>0.7670228910886175</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.406291194607492</v>
+        <v>4.458877120174572</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.165791572535222</v>
+        <v>-5.090905366565786</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.031921571451318</v>
+        <v>2.061876053839093</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6900657203730416</v>
+        <v>0.7777089296515076</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.512634057002979</v>
+        <v>4.565219982570059</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.21720199485593</v>
+        <v>-5.142315788886494</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.009143099648973</v>
+        <v>2.039097582036748</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6900657203730416</v>
+        <v>0.7777089296515076</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.510419754128918</v>
+        <v>4.563005679695998</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.296621446063682</v>
+        <v>-5.221735240094246</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.977278447240162</v>
+        <v>2.007232929627937</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6900657203730416</v>
+        <v>0.7777089296515076</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.510322882203208</v>
+        <v>4.562908807770287</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.3920844439809</v>
+        <v>-5.317198238011463</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.939087141631318</v>
+        <v>1.969041624019093</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6900657203730416</v>
+        <v>0.7777089296515076</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.510316775761251</v>
+        <v>4.562902701328331</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.432104442024683</v>
+        <v>-5.357218236055247</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.921175538976416</v>
+        <v>1.95113002136419</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6500457223292577</v>
+        <v>0.7376889316077238</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.484401173497591</v>
+        <v>4.536987099064671</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.487473604156877</v>
+        <v>-5.412587398187441</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.904761691871265</v>
+        <v>1.93471617425904</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6500457223292577</v>
+        <v>0.7376889316077238</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.490134991245318</v>
+        <v>4.542720916812398</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.532911383987704</v>
+        <v>-5.458025178018268</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.886124943281867</v>
+        <v>1.916079425669642</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6072007316510981</v>
+        <v>0.6948439409295641</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.463966360181355</v>
+        <v>4.516552285748435</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.444704549840126</v>
+        <v>-5.36981834387069</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.941282069791217</v>
+        <v>1.971236552178992</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6072007316510981</v>
+        <v>0.6948439409295641</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.483840753031674</v>
+        <v>4.536426678598754</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.268414325234819</v>
+        <v>-5.193528119265382</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.995498860158068</v>
+        <v>2.025453342545843</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6072007316510981</v>
+        <v>0.6948439409295641</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.467541453556402</v>
+        <v>4.520127379123482</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.085202662101723</v>
+        <v>-5.010316456132287</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.071214474875352</v>
+        <v>2.101168957263126</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6072007316510981</v>
+        <v>0.6948439409295641</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.469972403020448</v>
+        <v>4.522558328587527</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.013481215087872</v>
+        <v>-4.938595009118436</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.065694239528781</v>
+        <v>2.095648721916556</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6789221786649488</v>
+        <v>0.7665653879434148</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.478796457076648</v>
+        <v>4.531382382643727</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.991108189480166</v>
+        <v>-4.91622198351073</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.021559195693036</v>
+        <v>2.05151367808081</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6901779297778503</v>
+        <v>0.7778211390563163</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.43246565366556</v>
+        <v>4.485051579232639</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.024124485390911</v>
+        <v>-4.949238279421475</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.193550882214093</v>
+        <v>2.223505364601868</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6207405531110988</v>
+        <v>0.7083837623895648</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.576001432550864</v>
+        <v>4.628587358117944</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.012596849741302</v>
+        <v>-4.937710643771866</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.190083162302186</v>
+        <v>2.220037644689961</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6797412113124612</v>
+        <v>0.7673844205909273</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.603323053299931</v>
+        <v>4.655908978867011</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.109938351083671</v>
+        <v>-5.035052145114235</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.154814674287027</v>
+        <v>2.184769156674801</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6353210291469729</v>
+        <v>0.7229642384254389</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.580339056522426</v>
+        <v>4.632924982089506</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.063655334980409</v>
+        <v>-5.120908174454201</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.17457896292117</v>
+        <v>2.151677827131653</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6628149590431147</v>
+        <v>0.6805881691993039</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.59808649665295</v>
+        <v>4.608750422746663</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.046846410581138</v>
+        <v>-5.10409925005493</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.16372173450138</v>
+        <v>2.140820598711863</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6868810547314949</v>
+        <v>0.704654264887684</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.594945355886479</v>
+        <v>4.605609281980193</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.138228973146597</v>
+        <v>-5.195481812620389</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.137333220520246</v>
+        <v>2.114432084730729</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5954984921660367</v>
+        <v>0.6132717023222258</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.550280329392255</v>
+        <v>4.560944255485968</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.126522255159591</v>
+        <v>-5.183775094633383</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.244144165539316</v>
+        <v>2.2212430297498</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6072052101530431</v>
+        <v>0.6249784203092322</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.659432618008727</v>
+        <v>4.67009654410244</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.814748046659991</v>
+        <v>3.759506218149766</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.478376397875146</v>
+        <v>4.390086901996122</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.126522255159591</v>
+        <v>-5.183775094633383</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.244144165539316</v>
+        <v>2.2212430297498</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6072052101530431</v>
+        <v>0.6249784203092322</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.471440194861514</v>
+        <v>4.383150698982489</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>118.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.0%</t>
+          <t>-688.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.1%</t>
+          <t>-157.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>586.9%</t>
+          <t>588.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.0%</t>
+          <t>-307.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-167.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.406003594734996</v>
+        <v>-4.471806624920745</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.983953421664838</v>
+        <v>1.957632209590538</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9327776230411267</v>
+        <v>0.8669745928553765</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.306377857697259</v>
+        <v>4.266896039585809</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.36442585096593</v>
+        <v>-4.424037204154557</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.994271087073901</v>
+        <v>1.970426545798451</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9743553668101916</v>
+        <v>0.9147440136215653</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.325011071860136</v>
+        <v>4.28924425994696</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.405580970534151</v>
+        <v>-4.465192323722778</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.979689669430749</v>
+        <v>1.955845128155298</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9332002472419707</v>
+        <v>0.8735888940533444</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.302198630303339</v>
+        <v>4.266431818390163</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.337532407842621</v>
+        <v>-4.397143761031248</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.019760120385243</v>
+        <v>1.995915579109793</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.001248809933501</v>
+        <v>0.9416374567448742</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.35587879379614</v>
+        <v>4.320111981882964</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.569132801012122</v>
+        <v>-4.628744154200748</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.947322633291037</v>
+        <v>1.923478092015587</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.001248809933501</v>
+        <v>0.9416374567448742</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.376081463969734</v>
+        <v>4.340314652056558</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.587205309303734</v>
+        <v>-4.64681666249236</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.940093629974393</v>
+        <v>1.916249088698942</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.001248809933501</v>
+        <v>0.9416374567448742</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.376081463969734</v>
+        <v>4.340314652056558</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.762312141880178</v>
+        <v>-4.821923495068805</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.830302810537281</v>
+        <v>1.806458269261831</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.001248809933501</v>
+        <v>0.9416374567448742</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.336333377563201</v>
+        <v>4.300566565650024</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.731026121339723</v>
+        <v>-4.79063747452835</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.849839837750404</v>
+        <v>1.825995296474953</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.032534830473956</v>
+        <v>0.9729234772853296</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.362127608884414</v>
+        <v>4.326360796971238</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.578000729226439</v>
+        <v>-4.637612082415066</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.010220994168622</v>
+        <v>1.986376452893171</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.18556022258724</v>
+        <v>1.125948869398614</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.553113843725288</v>
+        <v>4.517347031812113</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.606308043099709</v>
+        <v>-4.665919396288336</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.186364293527606</v>
+        <v>2.162519752252155</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.18556022258724</v>
+        <v>1.125948869398614</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.740580068633581</v>
+        <v>4.704813256720405</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.772901268213231</v>
+        <v>-4.832512621401858</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.089129954836279</v>
+        <v>2.065285413560829</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.018966997473717</v>
+        <v>0.9593556442850912</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.610027084919549</v>
+        <v>4.574260273006374</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.749865474851665</v>
+        <v>-4.809476828040292</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.102020674842623</v>
+        <v>2.078176133567172</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.018966997473717</v>
+        <v>0.9593556442850912</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.613703487581267</v>
+        <v>4.577936675668091</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.720619494395969</v>
+        <v>-4.780230847584596</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.111337122148397</v>
+        <v>2.087492580872946</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.018966997473717</v>
+        <v>0.9593556442850912</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.611321542704762</v>
+        <v>4.575554730791587</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.82754504227382</v>
+        <v>-4.887156395462447</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.065860142154892</v>
+        <v>2.042015600879441</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9120414495958661</v>
+        <v>0.8524300964072399</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.544459453135687</v>
+        <v>4.508692641222511</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.972563600781069</v>
+        <v>-5.032174953969696</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.009281520895226</v>
+        <v>1.985436979619775</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7670228910886175</v>
+        <v>0.7074115378999913</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.458877120174572</v>
+        <v>4.423110308261396</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.090905366565786</v>
+        <v>-5.150516719754413</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.061876053839093</v>
+        <v>2.038031512563641</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7777089296515076</v>
+        <v>0.7180975764628814</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.565219982570059</v>
+        <v>4.529453170656883</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.142315788886494</v>
+        <v>-5.201927142075121</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.039097582036748</v>
+        <v>2.015253040761297</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7777089296515076</v>
+        <v>0.7180975764628814</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.563005679695998</v>
+        <v>4.527238867782822</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.221735240094246</v>
+        <v>-5.281346593282873</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.007232929627937</v>
+        <v>1.983388388352486</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7777089296515076</v>
+        <v>0.7180975764628814</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.562908807770287</v>
+        <v>4.527141995857112</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.317198238011463</v>
+        <v>-5.37680959120009</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.969041624019093</v>
+        <v>1.945197082743642</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7777089296515076</v>
+        <v>0.7180975764628814</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.562902701328331</v>
+        <v>4.527135889415155</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.357218236055247</v>
+        <v>-5.416829589243874</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.95113002136419</v>
+        <v>1.927285480088739</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7376889316077238</v>
+        <v>0.6780775784190975</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.536987099064671</v>
+        <v>4.501220287151495</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.412587398187441</v>
+        <v>-5.472198751376068</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.93471617425904</v>
+        <v>1.910871632983589</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7376889316077238</v>
+        <v>0.6780775784190975</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.542720916812398</v>
+        <v>4.506954104899222</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.458025178018268</v>
+        <v>-5.517636531206895</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.916079425669642</v>
+        <v>1.892234884394191</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6948439409295641</v>
+        <v>0.6352325877409379</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.516552285748435</v>
+        <v>4.480785473835259</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.36981834387069</v>
+        <v>-5.429429697059317</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.971236552178992</v>
+        <v>1.947392010903541</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6948439409295641</v>
+        <v>0.6352325877409379</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.536426678598754</v>
+        <v>4.500659866685578</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.193528119265382</v>
+        <v>-5.253139472454009</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.025453342545843</v>
+        <v>2.001608801270392</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6948439409295641</v>
+        <v>0.6352325877409379</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.520127379123482</v>
+        <v>4.484360567210306</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.010316456132287</v>
+        <v>-5.069927809320914</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.101168957263126</v>
+        <v>2.077324415987675</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6948439409295641</v>
+        <v>0.6352325877409379</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.522558328587527</v>
+        <v>4.486791516674351</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.938595009118436</v>
+        <v>-4.998206362307063</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.095648721916556</v>
+        <v>2.071804180641105</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7665653879434148</v>
+        <v>0.7069540347547886</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.531382382643727</v>
+        <v>4.495615570730551</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.91622198351073</v>
+        <v>-4.975833336699357</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.05151367808081</v>
+        <v>2.027669136805359</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7778211390563163</v>
+        <v>0.7182097858676901</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.485051579232639</v>
+        <v>4.449284767319464</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.949238279421475</v>
+        <v>-5.008849632610102</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.223505364601868</v>
+        <v>2.199660823326417</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7083837623895648</v>
+        <v>0.6487724092009386</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.628587358117944</v>
+        <v>4.592820546204768</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.937710643771866</v>
+        <v>-4.997321996960493</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.220037644689961</v>
+        <v>2.196193103414509</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7673844205909273</v>
+        <v>0.7077730674023011</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.655908978867011</v>
+        <v>4.620142166953835</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.035052145114235</v>
+        <v>-5.094663498302862</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.184769156674801</v>
+        <v>2.160924615399351</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7229642384254389</v>
+        <v>0.6633528852368127</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.632924982089506</v>
+        <v>4.59715817017633</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.120908174454201</v>
+        <v>-5.180519527642828</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.151677827131653</v>
+        <v>2.127833285856202</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6805881691993039</v>
+        <v>0.6209768160106777</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.608750422746663</v>
+        <v>4.572983610833488</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.10409925005493</v>
+        <v>-5.163710603243557</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.140820598711863</v>
+        <v>2.116976057436412</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.704654264887684</v>
+        <v>0.6450429116990578</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.605609281980193</v>
+        <v>4.569842470067018</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.71556459695019</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.195481812620389</v>
+        <v>-5.255093165809016</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.114432084730729</v>
+        <v>2.090587543455278</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6132717023222258</v>
+        <v>0.5536603491335996</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.560944255485968</v>
+        <v>4.525177443572792</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171925</v>
+        <v>3.673998560171926</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.183775094633383</v>
+        <v>-5.24338644782201</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.2212430297498</v>
+        <v>2.197398488474349</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6249784203092322</v>
+        <v>0.565367067120606</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.67009654410244</v>
+        <v>4.634329732189264</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.759506218149766</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.390086901996122</v>
+        <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.183775094633383</v>
+        <v>-5.273360283132764</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.2212430297498</v>
+        <v>2.188441293081452</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6249784203092322</v>
+        <v>0.565367067120606</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.383150698982489</v>
+        <v>4.637362070920669</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240904.xlsx
+++ b/tame_output/ON/bt/strategyON_20240904.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.9%</t>
+          <t>-689.0%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.0%</t>
+          <t>589.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.3%</t>
+          <t>-308.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.5%</t>
+          <t>-177.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.424037204154557</v>
+        <v>-4.459752498007783</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.970426545798451</v>
+        <v>1.956140428257161</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9147440136215653</v>
+        <v>0.8790287197683393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.28924425994696</v>
+        <v>4.267815083635025</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.465192323722778</v>
+        <v>-4.500907617576003</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.955845128155298</v>
+        <v>1.941559010614008</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8735888940533444</v>
+        <v>0.8378736002001184</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266431818390163</v>
+        <v>4.245002642078228</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.397143761031248</v>
+        <v>-4.432859054884474</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.995915579109793</v>
+        <v>1.981629461568502</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9416374567448742</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320111981882964</v>
+        <v>4.298682805571028</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.628744154200748</v>
+        <v>-4.664459448053974</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.923478092015587</v>
+        <v>1.909191974474296</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9416374567448742</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340314652056558</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.64681666249236</v>
+        <v>-4.682531956345586</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.916249088698942</v>
+        <v>1.901962971157652</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9416374567448742</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340314652056558</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.821923495068805</v>
+        <v>-4.857638788922031</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.806458269261831</v>
+        <v>1.79217215172054</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9416374567448742</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.300566565650024</v>
+        <v>4.279137389338089</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.79063747452835</v>
+        <v>-4.826352768381576</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.825995296474953</v>
+        <v>1.811709178933662</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9729234772853296</v>
+        <v>0.9372081834321035</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326360796971238</v>
+        <v>4.304931620659302</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.637612082415066</v>
+        <v>-4.673327376268292</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.986376452893171</v>
+        <v>1.972090335351881</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.125948869398614</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517347031812113</v>
+        <v>4.495917855500178</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.665919396288336</v>
+        <v>-4.701634690141562</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.162519752252155</v>
+        <v>2.148233634710865</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.125948869398614</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.704813256720405</v>
+        <v>4.683384080408469</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.832512621401858</v>
+        <v>-4.868227915255084</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.065285413560829</v>
+        <v>2.050999296019538</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9593556442850912</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574260273006374</v>
+        <v>4.552831096694439</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.809476828040292</v>
+        <v>-4.845192121893518</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.078176133567172</v>
+        <v>2.063890016025882</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9593556442850912</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.577936675668091</v>
+        <v>4.556507499356156</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.780230847584596</v>
+        <v>-4.815946141437822</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.087492580872946</v>
+        <v>2.073206463331656</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9593556442850912</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.575554730791587</v>
+        <v>4.554125554479652</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.887156395462447</v>
+        <v>-4.922871689315673</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.042015600879441</v>
+        <v>2.027729483338151</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8524300964072399</v>
+        <v>0.816714802554014</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.508692641222511</v>
+        <v>4.487263464910575</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.032174953969696</v>
+        <v>-5.067890247822922</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.985436979619775</v>
+        <v>1.971150862078485</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7074115378999913</v>
+        <v>0.6716962440467654</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.423110308261396</v>
+        <v>4.40168113194946</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.150516719754413</v>
+        <v>-5.186232013607639</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.038031512563641</v>
+        <v>2.023745395022351</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7180975764628814</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529453170656883</v>
+        <v>4.508023994344947</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.201927142075121</v>
+        <v>-5.237642435928347</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.015253040761297</v>
+        <v>2.000966923220007</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7180975764628814</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527238867782822</v>
+        <v>4.505809691470886</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.281346593282873</v>
+        <v>-5.317061887136099</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.983388388352486</v>
+        <v>1.969102270811196</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7180975764628814</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527141995857112</v>
+        <v>4.505712819545176</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.37680959120009</v>
+        <v>-5.412524885053316</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.945197082743642</v>
+        <v>1.930910965202352</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7180975764628814</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527135889415155</v>
+        <v>4.505706713103219</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.416829589243874</v>
+        <v>-5.4525448830971</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.927285480088739</v>
+        <v>1.912999362547449</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6780775784190975</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501220287151495</v>
+        <v>4.479791110839559</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.472198751376068</v>
+        <v>-5.507914045229294</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.910871632983589</v>
+        <v>1.896585515442298</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6780775784190975</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.506954104899222</v>
+        <v>4.485524928587286</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.517636531206895</v>
+        <v>-5.553351825060121</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.892234884394191</v>
+        <v>1.8779487668529</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6352325877409379</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.480785473835259</v>
+        <v>4.459356297523323</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.429429697059317</v>
+        <v>-5.445984789093479</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.947392010903541</v>
+        <v>1.940769974089876</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6352325877409379</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.500659866685578</v>
+        <v>4.479230690373642</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.253139472454009</v>
+        <v>-5.269694564488171</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.001608801270392</v>
+        <v>1.994986764456727</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6352325877409379</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.484360567210306</v>
+        <v>4.462931390898371</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.069927809320914</v>
+        <v>-5.086482901355076</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.077324415987675</v>
+        <v>2.070702379174011</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6352325877409379</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.486791516674351</v>
+        <v>4.465362340362416</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.998206362307063</v>
+        <v>-5.014761454341225</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.071804180641105</v>
+        <v>2.06518214382744</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7069540347547886</v>
+        <v>0.6712387409015627</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.495615570730551</v>
+        <v>4.474186394418616</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.975833336699357</v>
+        <v>-4.992388428733519</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.027669136805359</v>
+        <v>2.021047099991694</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7182097858676901</v>
+        <v>0.6824944920144642</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.449284767319464</v>
+        <v>4.427855591007528</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.008849632610102</v>
+        <v>-5.025404724644264</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.199660823326417</v>
+        <v>2.193038786512752</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6487724092009386</v>
+        <v>0.6130571153477127</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.592820546204768</v>
+        <v>4.571391369892833</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.997321996960493</v>
+        <v>-5.013877088994655</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.196193103414509</v>
+        <v>2.189571066600845</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7077730674023011</v>
+        <v>0.6720577735490751</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.620142166953835</v>
+        <v>4.598712990641899</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.094663498302862</v>
+        <v>-5.111218590337024</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.160924615399351</v>
+        <v>2.154302578585686</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6633528852368127</v>
+        <v>0.6276375913835868</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.59715817017633</v>
+        <v>4.575728993864395</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.180519527642828</v>
+        <v>-5.19707461967699</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.127833285856202</v>
+        <v>2.121211249042537</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6209768160106777</v>
+        <v>0.5852615221574518</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.572983610833488</v>
+        <v>4.551554434521552</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.163710603243557</v>
+        <v>-5.191746287351128</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.116976057436412</v>
+        <v>2.105761783793384</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6450429116990578</v>
+        <v>0.5843414691995147</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.569842470067018</v>
+        <v>4.533421604567292</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71556459695019</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.255093165809016</v>
+        <v>-5.283128849916586</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.090587543455278</v>
+        <v>2.07937326981225</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5536603491335996</v>
+        <v>0.4929589066340565</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.525177443572792</v>
+        <v>4.488756578073066</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.24338644782201</v>
+        <v>-5.307187310612465</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.197398488474349</v>
+        <v>2.171878143358167</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.565367067120606</v>
+        <v>0.4689004459381776</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.634329732189264</v>
+        <v>4.576449759479807</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.759506218149766</v>
+        <v>3.700598804920795</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.273360283132764</v>
+        <v>-5.274743635044064</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.188441293081452</v>
+        <v>2.187887952316932</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.565367067120606</v>
+        <v>0.4689004459381776</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.637362070920669</v>
+        <v>4.579482098211212</v>
       </c>
     </row>
   </sheetData>
